--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.73654303430358</v>
+        <v>2.557188243074331</v>
       </c>
       <c r="D2" t="n">
-        <v>12.32900299447778</v>
+        <v>2.003462986602639</v>
       </c>
       <c r="E2" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F2" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.89071441668048</v>
+        <v>5.669741092710578</v>
       </c>
       <c r="D3" t="n">
-        <v>31.54941622846665</v>
+        <v>5.12678013712583</v>
       </c>
       <c r="E3" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F3" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.57432093262365</v>
+        <v>9.843327151551343</v>
       </c>
       <c r="D4" t="n">
-        <v>32.38271143681456</v>
+        <v>5.262190608482366</v>
       </c>
       <c r="E4" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F4" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.19126220605042</v>
+        <v>6.043580108483193</v>
       </c>
       <c r="D5" t="n">
-        <v>38.49389664869017</v>
+        <v>6.255258205412153</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F5" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.51127261762015</v>
+        <v>4.633081800363275</v>
       </c>
       <c r="D6" t="n">
-        <v>28.90038248737446</v>
+        <v>4.69631215419835</v>
       </c>
       <c r="E6" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F6" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.59144875085892</v>
+        <v>4.971110422014575</v>
       </c>
       <c r="D7" t="n">
-        <v>30.87886950000895</v>
+        <v>5.017816293751454</v>
       </c>
       <c r="E7" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F7" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.99621585911593</v>
+        <v>4.061885077106339</v>
       </c>
       <c r="D8" t="n">
-        <v>22.74448869900995</v>
+        <v>3.695979413589116</v>
       </c>
       <c r="E8" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F8" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.72431468666349</v>
+        <v>4.505201136582818</v>
       </c>
       <c r="D9" t="n">
-        <v>28.35689966571065</v>
+        <v>4.607996195677981</v>
       </c>
       <c r="E9" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F9" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.0153516996514</v>
+        <v>7.964994651193353</v>
       </c>
       <c r="D10" t="n">
-        <v>14.32912096795816</v>
+        <v>2.328482157293202</v>
       </c>
       <c r="E10" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F10" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.07238054195793</v>
+        <v>7.324261838068164</v>
       </c>
       <c r="D11" t="n">
-        <v>8.173952754496788</v>
+        <v>1.328267322605728</v>
       </c>
       <c r="E11" t="n">
-        <v>12.41177296846274</v>
+        <v>2.016913107375196</v>
       </c>
       <c r="F11" t="n">
-        <v>9.501610319169053</v>
+        <v>1.544011676864971</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
